--- a/docs/StructureDefinition-BRRegistroPrescricaoMedicamento.xlsx
+++ b/docs/StructureDefinition-BRRegistroPrescricaoMedicamento.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-05T10:09:20-03:00</t>
+    <t>2026-06-16T17:47:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -370,7 +370,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -790,7 +790,7 @@
     <t>High-level kind of a clinical document at a macro level.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -877,7 +877,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -922,7 +922,7 @@
     <t>Composition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1174,7 +1174,7 @@
     <t>Composition.attester.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1199,7 +1199,7 @@
     <t>Composition.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1285,7 +1285,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(Composition)</t>
+Reference(Composition|4.0.1)</t>
   </si>
   <si>
     <t>Target of the relationship</t>
@@ -1376,7 +1376,7 @@
     <t>Composition.event.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1455,13 +1455,13 @@
     <t>Classification of a section of a composition/document.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/doc-section-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/doc-section-codes|4.0.1</t>
   </si>
   <si>
     <t>Composition.section.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Device|Patient|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1547,7 +1547,7 @@
     <t>What order applies to the items in the entry.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -1615,7 +1615,7 @@
     <t>If a section is empty, why it is empty.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>

--- a/docs/StructureDefinition-BRRegistroPrescricaoMedicamento.xlsx
+++ b/docs/StructureDefinition-BRRegistroPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:16:11-03:00</t>
+    <t>2026-08-24T11:43:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRRegistroPrescricaoMedicamento.xlsx
+++ b/docs/StructureDefinition-BRRegistroPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T11:43:54-03:00</t>
+    <t>2026-09-15T15:40:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRRegistroPrescricaoMedicamento.xlsx
+++ b/docs/StructureDefinition-BRRegistroPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:40:41-03:00</t>
+    <t>2026-09-23T09:07:03-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRRegistroPrescricaoMedicamento.xlsx
+++ b/docs/StructureDefinition-BRRegistroPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:07:03-03:00</t>
+    <t>2026-09-30T18:22:16-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
